--- a/output/pdf_financials_xlsx/LILL.P.xlsx
+++ b/output/pdf_financials_xlsx/LILL.P.xlsx
@@ -2762,13 +2762,13 @@
         <v>0.051146</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.051146</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.051146</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.051146</v>
       </c>
     </row>
     <row r="93">
@@ -4088,7 +4088,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/LILL.P.xlsx
+++ b/output/pdf_financials_xlsx/LILL.P.xlsx
@@ -1420,19 +1420,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.105</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.200142</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.154963</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.118751</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.07613399999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1464,19 +1464,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.105</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.200142</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.154963</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.118751</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.07613399999999999</v>
       </c>
     </row>
     <row r="37">
@@ -3897,7 +3897,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/LILL.P.xlsx
+++ b/output/pdf_financials_xlsx/LILL.P.xlsx
@@ -1100,10 +1100,8 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>-0.005</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-0.109653</v>
@@ -2894,10 +2892,8 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-0.005</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>-0.109653</v>
@@ -2918,10 +2914,8 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
         <v>0</v>
@@ -2942,10 +2936,8 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>0</v>
@@ -2966,10 +2958,8 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C102" s="3" t="n">
         <v>0</v>
@@ -2990,10 +2980,8 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C103" s="3" t="n">
         <v>0</v>
@@ -3014,10 +3002,8 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>0.005</v>
       </c>
       <c r="C104" s="3" t="n">
         <v>0.009146</v>
@@ -3038,10 +3024,8 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C105" s="3" t="n">
         <v>0</v>
@@ -3062,10 +3046,8 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0.005</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>0.009146</v>
@@ -3086,10 +3068,8 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C107" s="3" t="n">
         <v>0.038168</v>
@@ -3110,10 +3090,8 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C108" s="3" t="n">
         <v>0</v>
@@ -3134,10 +3112,8 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C109" s="3" t="n">
         <v>0</v>
@@ -3158,10 +3134,8 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
         <v>0</v>
@@ -3182,10 +3156,8 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -3206,10 +3178,8 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
         <v>0</v>
@@ -3230,10 +3200,8 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C113" s="3" t="n">
         <v>0</v>
@@ -3254,10 +3222,8 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C114" s="3" t="n">
         <v>0</v>
@@ -3278,10 +3244,8 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>0</v>
@@ -3302,10 +3266,8 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C116" s="3" t="n">
         <v>0</v>
@@ -3326,10 +3288,8 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C117" s="3" t="n">
         <v>0</v>
@@ -3350,10 +3310,8 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
         <v>0</v>
@@ -3404,10 +3362,8 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C120" s="3" t="n">
         <v>0</v>
@@ -3428,10 +3384,8 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C121" s="3" t="n">
         <v>0</v>
@@ -3452,10 +3406,8 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C122" s="3" t="n">
         <v>0</v>
@@ -3476,10 +3428,8 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C123" s="3" t="n">
         <v>0</v>
@@ -3500,10 +3450,8 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C124" s="3" t="n">
         <v>0</v>
@@ -3524,10 +3472,8 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C125" s="3" t="n">
         <v>0</v>
@@ -3548,10 +3494,8 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C126" s="3" t="n">
         <v>0</v>
@@ -3604,10 +3548,8 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C128" s="3" t="n">
         <v>0</v>
@@ -3628,10 +3570,8 @@
           <t>Cash Flow from Financing</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B129" s="3" t="n">
+        <v>0.105</v>
       </c>
       <c r="C129" s="3" t="n">
         <v>0.157481</v>
@@ -3690,10 +3630,8 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C131" s="3" t="n">
         <v>0</v>
@@ -3714,10 +3652,8 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>0.105</v>
       </c>
       <c r="C132" s="3" t="n">
         <v>0.095142</v>
@@ -3770,10 +3706,8 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -5530,10 +5464,8 @@
           <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E44" s="5" t="n">
+        <v>-0.005</v>
       </c>
       <c r="F44" s="5" t="n">
         <v>-0.109653</v>
@@ -5776,10 +5708,8 @@
           <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E50" s="5" t="n">
+        <v>0.005</v>
       </c>
       <c r="F50" s="5" t="n">
         <v>0.009146</v>
@@ -6019,11 +5949,13 @@
           <t>Proceeds from shares issued</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>0.105</v>
       </c>
       <c r="F56" s="5" t="n">
         <v>0.157481</v>
@@ -6065,10 +5997,8 @@
           <t>FinancingCashFlow</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E57" s="5" t="n">
+        <v>0.105</v>
       </c>
       <c r="F57" s="5" t="n">
         <v>0.157481</v>
@@ -6110,10 +6040,8 @@
           <t>ChangesInCash</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E58" s="5" t="n">
+        <v>0.105</v>
       </c>
       <c r="F58" s="5" t="n">
         <v>0.095142</v>
@@ -6188,10 +6116,8 @@
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E60" s="5" t="n">
+        <v>0.105</v>
       </c>
       <c r="F60" s="5" t="n">
         <v>0.200142</v>
